--- a/planning/원두주문_덤_이익.xlsx
+++ b/planning/원두주문_덤_이익.xlsx
@@ -92,7 +92,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -129,6 +129,15 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -494,7 +503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O36"/>
+  <dimension ref="A1:O38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -524,16 +533,22 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>노란 칸(파란 글씨)을 바꾸면 다시 계산돼요. 자료: 대표 PC 통합앱 정리 파일(2026-10-28). 1봉 원가 = 생두 원가 + 포장재(인건비·고정비 제외).</t>
-        </is>
-      </c>
-    </row>
+          <t>노란 칸을 바꾸면 다시 계산돼요. 자료: 대표 PC 통합앱 정리 파일(10/28). 코스모스·구수·보통 원가는 통합앱 배합의 생두 단가 기준이라, 자사몰 배합(현재 기준)과 생두가 달라 실제와 차이가 날 수 있어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>입력값</t>
         </is>
       </c>
+      <c r="E4" s="14" t="inlineStr">
+        <is>
+          <t>허벌 원가 입력</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -549,6 +564,23 @@
           <t>대표·클로드 안(10/28)</t>
         </is>
       </c>
+      <c r="E5" s="15" t="inlineStr">
+        <is>
+          <t>라 에스메랄다 생두(원/kg)</t>
+        </is>
+      </c>
+      <c r="G5" s="16" t="n">
+        <v>52000</v>
+      </c>
+      <c r="I5" s="15" t="inlineStr">
+        <is>
+          <t>볶은 원두 kg당</t>
+        </is>
+      </c>
+      <c r="J5" s="17">
+        <f>ROUND((G5*G7+G6*(1-G7))/(1-G8),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -564,6 +596,19 @@
           <t>드립백_원가표.xlsx 4종 평균 3,309÷4</t>
         </is>
       </c>
+      <c r="E6" s="15" t="inlineStr">
+        <is>
+          <t>엘 포르베니르 생두(원/kg)</t>
+        </is>
+      </c>
+      <c r="G6" s="16" t="n">
+        <v>28000</v>
+      </c>
+      <c r="I6" s="18" t="inlineStr">
+        <is>
+          <t>배합은 대표 계산(70:30). 라벨은 67:33 — 확인 필요. 손실률 15%는 다른 블렌드(13.5~16.3%) 기준 추정</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -579,6 +624,14 @@
           <t>아임웹: 다른 할인과 중복 안 됨</t>
         </is>
       </c>
+      <c r="E7" s="15" t="inlineStr">
+        <is>
+          <t>에스메랄다 비율</t>
+        </is>
+      </c>
+      <c r="G7" s="19" t="n">
+        <v>0.7</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -594,6 +647,14 @@
           <t>5만 원 이상 무료</t>
         </is>
       </c>
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>로스팅 손실률(추정)</t>
+        </is>
+      </c>
+      <c r="G8" s="19" t="n">
+        <v>0.15</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -606,6 +667,7 @@
       </c>
       <c r="C9" s="6" t="inlineStr"/>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
@@ -676,6 +738,7 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
@@ -1459,43 +1522,174 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="20" t="inlineStr">
+        <is>
+          <t>허벌 블렌드</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="inlineStr">
+        <is>
+          <t>200g</t>
+        </is>
+      </c>
+      <c r="C30" s="20" t="n">
+        <v>26000</v>
+      </c>
+      <c r="D30" s="20">
+        <f>ROUND(C30/1.1,0)</f>
+        <v/>
+      </c>
+      <c r="E30" s="20">
+        <f>ROUND($J$5*200/1000+636,0)</f>
+        <v/>
+      </c>
+      <c r="F30" s="20" t="inlineStr">
+        <is>
+          <t>극소</t>
+        </is>
+      </c>
+      <c r="G30" s="20">
+        <f>VLOOKUP(F30,$A$13:$C$15,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="H30" s="20">
+        <f>VLOOKUP(F30,$A$13:$C$15,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="I30" s="20">
+        <f>$B$5*$B$6</f>
+        <v/>
+      </c>
+      <c r="J30" s="17">
+        <f>D30-E30-G30-H30-I30</f>
+        <v/>
+      </c>
+      <c r="K30" s="21">
+        <f>J30/D30</f>
+        <v/>
+      </c>
+      <c r="L30" s="20">
+        <f>IF(C30&gt;=10000,ROUND((C30-$B$7)/1.1,0),D30)-E30-G30-H30-I30</f>
+        <v/>
+      </c>
+      <c r="M30" s="20">
+        <f>ROUND(C30*0.9/1.1,0)-E30-G30-H30</f>
+        <v/>
+      </c>
+      <c r="N30" s="20">
+        <f>IF(C30&gt;=$B$9,D30-G30,D30+ROUND($B$8/1.1,0)-G30)-E30-H30</f>
+        <v/>
+      </c>
+      <c r="O30" s="22" t="inlineStr">
+        <is>
+          <t>추정: 생두 가중평균 ÷ (1−손실률) + 포장재. 판매가는 대표 10/28 결정</t>
+        </is>
+      </c>
+    </row>
     <row r="31">
-      <c r="A31" s="3" t="inlineStr">
+      <c r="A31" s="20" t="inlineStr">
+        <is>
+          <t>허벌 블렌드</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="C31" s="20" t="n">
+        <v>52000</v>
+      </c>
+      <c r="D31" s="20">
+        <f>ROUND(C31/1.1,0)</f>
+        <v/>
+      </c>
+      <c r="E31" s="20">
+        <f>ROUND($J$5*500/1000+751,0)</f>
+        <v/>
+      </c>
+      <c r="F31" s="20" t="inlineStr">
+        <is>
+          <t>소</t>
+        </is>
+      </c>
+      <c r="G31" s="20">
+        <f>VLOOKUP(F31,$A$13:$C$15,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="H31" s="20">
+        <f>VLOOKUP(F31,$A$13:$C$15,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="I31" s="20">
+        <f>$B$5*$B$6</f>
+        <v/>
+      </c>
+      <c r="J31" s="17">
+        <f>D31-E31-G31-H31-I31</f>
+        <v/>
+      </c>
+      <c r="K31" s="21">
+        <f>J31/D31</f>
+        <v/>
+      </c>
+      <c r="L31" s="20">
+        <f>IF(C31&gt;=10000,ROUND((C31-$B$7)/1.1,0),D31)-E31-G31-H31-I31</f>
+        <v/>
+      </c>
+      <c r="M31" s="20">
+        <f>ROUND(C31*0.9/1.1,0)-E31-G31-H31</f>
+        <v/>
+      </c>
+      <c r="N31" s="20">
+        <f>IF(C31&gt;=$B$9,D31-G31,D31+ROUND($B$8/1.1,0)-G31)-E31-H31</f>
+        <v/>
+      </c>
+      <c r="O31" s="22" t="inlineStr">
+        <is>
+          <t>추정: 생두 가중평균 ÷ (1−손실률) + 포장재. 판매가는 대표 10/28 결정</t>
+        </is>
+      </c>
+    </row>
+    <row r="32"/>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>읽는 법</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="13" t="inlineStr">
-        <is>
-          <t>· 카페쇼 이익 = 공급가액 − 1봉 원가 − 택배비 − 박스 − 덤 드립백. 무료배송이라 택배비는 가치커피 부담.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="13" t="inlineStr">
-        <is>
-          <t>· 가입 쿠폰은 다른 할인과 중복이 안 되는데, 덤 방식은 할인이 아니라서 1만 원 이상이면 쿠폰을 같이 쓸 수 있어요.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="13" t="inlineStr">
         <is>
-          <t>· 10% 할인 칸은 비교용(덤 없음). 평소 자사몰 칸은 5만 원 미만이면 고객이 배송비 3,000원을 내는 경우.</t>
+          <t>· 확정(10/28): 카페쇼 원두 주문은 무료배송 + 주문 1건당 드립백 2개 덤. 이익 = 공급가액 − 1봉 원가 − 택배비 − 박스 − 덤.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="13" t="inlineStr">
         <is>
-          <t>· 허벌은 자사몰 소매 상품이 없어 뺐어요(B2B 1kg 62,000원만 있음). 카페쇼에서 팔려면 상품 등록과 소매가 결정이 필요해요.</t>
+          <t>· 가입 쿠폰은 다른 할인과 중복이 안 되는데, 덤 방식은 할인이 아니라서 1만 원 이상이면 쿠폰을 같이 쓸 수 있어요.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="13" t="inlineStr">
+        <is>
+          <t>· 10% 할인 칸은 비교용(덤 없음). 평소 자사몰 칸은 5만 원 미만이면 고객이 배송비 3,000원을 내는 경우.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="13" t="inlineStr">
+        <is>
+          <t>· 허벌 판매가(200g 26,000 / 500g 52,000)는 대표 10/28 결정. 원가는 추정이라 노란 칸을 실제 값으로 바꾸세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="13" t="inlineStr">
         <is>
           <t>· 원가에 인건비·로스팅 가스비·카드/페이 수수료는 없어요. 생두·포장재·택배 단가의 부가세 포함 여부는 자료 없음.</t>
         </is>

--- a/planning/원두주문_덤_이익.xlsx
+++ b/planning/원두주문_덤_이익.xlsx
@@ -533,11 +533,10 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>노란 칸을 바꾸면 다시 계산돼요. 자료: 대표 PC 통합앱 정리 파일(10/28). 코스모스·구수·보통 원가는 통합앱 배합의 생두 단가 기준이라, 자사몰 배합(현재 기준)과 생두가 달라 실제와 차이가 날 수 있어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+          <t>노란 칸을 바꾸면 다시 계산돼요. 자료: 대표 PC 통합앱 정리 파일(10/28). 코스모스·구수·보통 원가는 통합앱 값을 정확한 값으로 씀(대표 10/28).</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -606,7 +605,7 @@
       </c>
       <c r="I6" s="18" t="inlineStr">
         <is>
-          <t>배합은 대표 계산(70:30). 라벨은 67:33 — 확인 필요. 손실률 15%는 다른 블렌드(13.5~16.3%) 기준 추정</t>
+          <t>배합은 라벨 기준 67:33(대표 10/28). 손실률 15%는 다른 블렌드(13.5~16.3%) 기준 추정</t>
         </is>
       </c>
     </row>
@@ -630,7 +629,7 @@
         </is>
       </c>
       <c r="G7" s="19" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="8">
@@ -667,7 +666,6 @@
       </c>
       <c r="C9" s="6" t="inlineStr"/>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
@@ -738,7 +736,6 @@
         </is>
       </c>
     </row>
-    <row r="17"/>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
@@ -1652,7 +1649,6 @@
         </is>
       </c>
     </row>
-    <row r="32"/>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>

--- a/planning/원두주문_덤_이익.xlsx
+++ b/planning/원두주문_덤_이익.xlsx
@@ -543,6 +543,14 @@
           <t>입력값</t>
         </is>
       </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>대표 10/28 수정: 2개 → 1개(오버). 문구 "드립백 증정"</t>
+        </is>
+      </c>
       <c r="E4" s="14" t="inlineStr">
         <is>
           <t>허벌 원가 입력</t>
@@ -556,11 +564,11 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>2</v>
+        <v>773</v>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>대표·클로드 안(10/28)</t>
+          <t>드립백_원가표.xlsx 4종 평균 3,093÷4 (10/28 허벌 블렌드 반영)</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">

--- a/planning/원두주문_덤_이익.xlsx
+++ b/planning/원두주문_덤_이익.xlsx
@@ -543,14 +543,6 @@
           <t>입력값</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>대표 10/28 수정: 2개 → 1개(오버). 문구 "드립백 증정"</t>
-        </is>
-      </c>
       <c r="E4" s="14" t="inlineStr">
         <is>
           <t>허벌 원가 입력</t>
@@ -564,11 +556,11 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>773</v>
+        <v>1</v>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>드립백_원가표.xlsx 4종 평균 3,093÷4 (10/28 허벌 블렌드 반영)</t>
+          <t>대표 10/28 수정: 2개 → 1개. 문구 "드립백 증정"</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
@@ -596,11 +588,11 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>827</v>
+        <v>773</v>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>드립백_원가표.xlsx 4종 평균 3,309÷4</t>
+          <t>드립백_원가표.xlsx 4종 평균 3,093÷4 (10/28 허벌 블렌드 반영)</t>
         </is>
       </c>
       <c r="E6" s="15" t="inlineStr">

--- a/planning/원두주문_덤_이익.xlsx
+++ b/planning/원두주문_덤_이익.xlsx
@@ -537,6 +537,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -592,7 +593,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>드립백_원가표.xlsx 4종 평균 3,093÷4 (10/28 허벌 블렌드 반영)</t>
+          <t>드립백_원가표.xlsx 4종 평균 3,093÷4 (10/28 허벌 블랜드 반영)</t>
         </is>
       </c>
       <c r="E6" s="15" t="inlineStr">
@@ -605,7 +606,7 @@
       </c>
       <c r="I6" s="18" t="inlineStr">
         <is>
-          <t>배합은 라벨 기준 67:33(대표 10/28). 손실률 15%는 다른 블렌드(13.5~16.3%) 기준 추정</t>
+          <t>배합은 라벨 기준 67:33(대표 10/28). 손실률 15%는 다른 블랜드(13.5~16.3%) 기준 추정</t>
         </is>
       </c>
     </row>
@@ -666,6 +667,7 @@
       </c>
       <c r="C9" s="6" t="inlineStr"/>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
@@ -736,6 +738,7 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
@@ -1450,7 +1453,7 @@
       </c>
       <c r="O28" s="6" t="inlineStr">
         <is>
-          <t>추정: 생두 52,000원/kg, 로스팅 손실 15%(블렌드 3종 13.5~16.3% 사이로 가정)</t>
+          <t>추정: 생두 52,000원/kg, 로스팅 손실 15%(블랜드 3종 13.5~16.3% 사이로 가정)</t>
         </is>
       </c>
     </row>
@@ -1522,7 +1525,7 @@
     <row r="30">
       <c r="A30" s="20" t="inlineStr">
         <is>
-          <t>허벌 블렌드</t>
+          <t>허벌 블랜드</t>
         </is>
       </c>
       <c r="B30" s="20" t="inlineStr">
@@ -1587,7 +1590,7 @@
     <row r="31">
       <c r="A31" s="20" t="inlineStr">
         <is>
-          <t>허벌 블렌드</t>
+          <t>허벌 블랜드</t>
         </is>
       </c>
       <c r="B31" s="20" t="inlineStr">
@@ -1649,6 +1652,7 @@
         </is>
       </c>
     </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
